--- a/artfynd/A 55410-2025 artfynd.xlsx
+++ b/artfynd/A 55410-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910849</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55410-2025 artfynd.xlsx
+++ b/artfynd/A 55410-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910849</v>
       </c>
       <c r="B2" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55410-2025 artfynd.xlsx
+++ b/artfynd/A 55410-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910849</v>
       </c>
       <c r="B2" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55410-2025 artfynd.xlsx
+++ b/artfynd/A 55410-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910849</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
+        <v>56922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55410-2025 artfynd.xlsx
+++ b/artfynd/A 55410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910849</v>
+        <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,26 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Parlahöjden Jätpe, Dlr</t>
+          <t>Parlahöjden spillkråka, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498108</v>
+        <v>498198</v>
       </c>
       <c r="R2" t="n">
-        <v>6692245</v>
+        <v>6692339</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,6 +753,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stort hål i gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,6 +779,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129910849</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Parlahöjden Jätpe, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>498108</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6692245</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
